--- a/data/trans_orig/IP2901-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>49374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69852</t>
+          <t>70365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84329</t>
+          <t>84495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81876</t>
+          <t>81655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97277</t>
+          <t>97314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>157437</t>
+          <t>157759</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178094</t>
+          <t>178550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52598</t>
+          <t>53501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44968</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82248</t>
+          <t>82276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110223</t>
+          <t>110652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27564</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180990</t>
+          <t>179957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203054</t>
+          <t>203179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164074</t>
+          <t>164575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187982</t>
+          <t>188023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352620</t>
+          <t>351545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>383529</t>
+          <t>382771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33191</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40492</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61696</t>
+          <t>61607</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83522</t>
+          <t>83987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>92401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108370</t>
+          <t>108482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179385</t>
+          <t>180830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203641</t>
+          <t>204391</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25461</t>
+          <t>25079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>44863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57428</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81619</t>
+          <t>81161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139233</t>
+          <t>137844</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156903</t>
+          <t>156994</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147332</t>
+          <t>147947</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>167445</t>
+          <t>166318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293944</t>
+          <t>293540</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>319614</t>
+          <t>319248</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>105748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>135276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>150193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230396</t>
+          <t>232945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275478</t>
+          <t>278081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>60056</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73828</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>101346</t>
+          <t>103102</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492897</t>
+          <t>494202</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>528087</t>
+          <t>527609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>506028</t>
+          <t>506989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>542538</t>
+          <t>544127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1013630</t>
+          <t>1010789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1061918</t>
+          <t>1061822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24770</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53751</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76131</t>
+          <t>74887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87246</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106251</t>
+          <t>105722</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87501</t>
+          <t>87609</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105960</t>
+          <t>105519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>179453</t>
+          <t>181052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205868</t>
+          <t>207035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39120</t>
+          <t>39417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59124</t>
+          <t>60391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>59325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82774</t>
+          <t>83045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102638</t>
+          <t>104196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134829</t>
+          <t>136004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>29359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48435</t>
+          <t>49062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158883</t>
+          <t>158375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180068</t>
+          <t>180044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160272</t>
+          <t>159682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186111</t>
+          <t>186129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>323872</t>
+          <t>322321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>358366</t>
+          <t>358215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44930</t>
+          <t>44072</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29987</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62493</t>
+          <t>62485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86288</t>
+          <t>85590</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36202</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98157</t>
+          <t>99061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118302</t>
+          <t>118351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92742</t>
+          <t>92687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112418</t>
+          <t>112349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196826</t>
+          <t>198744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224197</t>
+          <t>225518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>46333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37490</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56514</t>
+          <t>56411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70579</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98255</t>
+          <t>96032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15547</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112862</t>
+          <t>111621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132219</t>
+          <t>131757</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110769</t>
+          <t>110369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131154</t>
+          <t>130911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>228545</t>
+          <t>228565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>256615</t>
+          <t>257471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133694</t>
+          <t>134541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169164</t>
+          <t>170311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168476</t>
+          <t>168533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208834</t>
+          <t>209425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313820</t>
+          <t>313839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366123</t>
+          <t>365110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73597</t>
+          <t>73146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101428</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137235</t>
+          <t>137365</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>477575</t>
+          <t>479691</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>516583</t>
+          <t>518918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>473417</t>
+          <t>470960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>516590</t>
+          <t>513957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>961303</t>
+          <t>961615</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1020206</t>
+          <t>1020835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39165</t>
+          <t>40148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99396</t>
+          <t>99897</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112782</t>
+          <t>113485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81567</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96388</t>
+          <t>96657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185457</t>
+          <t>184242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>206577</t>
+          <t>205565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35412</t>
+          <t>34780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68824</t>
+          <t>69045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20395</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46383</t>
+          <t>45406</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156411</t>
+          <t>156276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174622</t>
+          <t>174405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191987</t>
+          <t>191154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212439</t>
+          <t>211261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353674</t>
+          <t>353340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>381432</t>
+          <t>380770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>41627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31879</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45933</t>
+          <t>45033</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>67863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45709</t>
+          <t>45953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119695</t>
+          <t>119898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140824</t>
+          <t>140316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137854</t>
+          <t>137693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155715</t>
+          <t>155346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263993</t>
+          <t>263085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291197</t>
+          <t>291069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47338</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50816</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74758</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>32440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>106521</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125368</t>
+          <t>126282</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118675</t>
+          <t>118862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>136067</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231477</t>
+          <t>230499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>259421</t>
+          <t>256925</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125865</t>
+          <t>125738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82312</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111990</t>
+          <t>112009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183535</t>
+          <t>185984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228850</t>
+          <t>226982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46206</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>103674</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>139203</t>
+          <t>137127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>503032</t>
+          <t>500158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>537980</t>
+          <t>537504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>547655</t>
+          <t>548146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>584137</t>
+          <t>584236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1061791</t>
+          <t>1062684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1112951</t>
+          <t>1111404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2901-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19876</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13892</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27697</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19760</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13442</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26703</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13673</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27540</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19876</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14264</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27778</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30808</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49374</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13612</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6451</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11167</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11517</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8464</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14127</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21902</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90445</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82064</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97173</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69,09%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>81,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>77990</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>70365</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>84495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>69798</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>84316</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>74,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>67,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>90445</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>81655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97314</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>76,14%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>157759</t>
+          <t>158526</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178550</t>
+          <t>178195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>118786</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>118786</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118786</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>104201</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>104201</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>104201</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>118786</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>118786</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>118786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54281</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45170</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66290</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>41853</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33081</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53501</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32874</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>52247</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54281</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>43715</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>65328</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82276</t>
+          <t>81838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110652</t>
+          <t>110983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20448</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14406</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28720</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>17491</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11881</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>25168</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11892</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>25406</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20448</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>28065</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>48547</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>176214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>163633</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>186548</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>192386</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>179957</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>203179</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>181138</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>202488</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>176214</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>164575</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>188023</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351545</t>
+          <t>353718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>382771</t>
+          <t>384811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>250942</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>250942</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>250942</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>251730</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>251730</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>251730</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>250942</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>250942</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>250942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25177</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18166</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32618</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25301</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18486</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19055</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33190</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>20,42%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>26,22%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25177</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19007</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33524</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61607</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10794</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6602</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16147</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6702</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11311</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12367</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10794</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6312</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16951</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>100763</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>92265</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>108706</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>91921</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83987</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>99801</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83974</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>100080</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>100763</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>92401</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>108482</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180830</t>
+          <t>180436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204391</t>
+          <t>203100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>123925</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>123925</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>123925</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35425</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27516</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44491</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33026</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25079</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42864</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24775</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>35425</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28158</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57094</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81161</t>
+          <t>80237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8969</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14544</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7502</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4148</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12618</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12916</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8969</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4931</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>15152</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158290</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148220</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>166458</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>78,1%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>73,13%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>82,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>148596</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>137844</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>156994</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>137971</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>157568</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>78,57%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>72,89%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158290</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>147947</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>166318</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293540</t>
+          <t>292894</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>319248</t>
+          <t>319260</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202684</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>202684</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>202684</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>189124</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>189124</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>189124</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>202684</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>202684</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>202684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>134759</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>119526</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>152971</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>119941</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>105748</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>135276</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>105736</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>137502</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>17,93%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>134759</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>117588</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>150193</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232945</t>
+          <t>231531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278081</t>
+          <t>279211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>38025</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60303</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>38146</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>29718</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>49112</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>29670</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>47914</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>48675</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>38277</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60056</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73967</t>
+          <t>72659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103102</t>
+          <t>101493</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>525713</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>507713</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>544783</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>74,13%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>71,59%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>762</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>510893</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>494202</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>527609</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>493259</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>527277</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>76,37%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>525713</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>506989</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>544127</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1010789</t>
+          <t>1009562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1061822</t>
+          <t>1061572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>709147</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>709147</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709147</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>668980</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>668980</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>668980</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>709147</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>709147</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709147</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31776</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24701</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41326</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32119</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24695</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40247</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24337</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40767</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31776</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24142</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>40423</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74887</t>
+          <t>77000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17028</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11667</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24514</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17838</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12692</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25758</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12526</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25627</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11366</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25423</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>26409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>96586</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>87006</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>105552</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>59,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>72,6%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>96805</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>87809</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>105722</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>87776</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>106062</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>65,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>59,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>96586</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>87609</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>105519</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181052</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>207035</t>
+          <t>205394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145390</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145390</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145390</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>145390</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>145390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59308</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>48271</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39417</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>60391</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38614</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>59358</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70237</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>59325</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>83045</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104196</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136004</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14424</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28891</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16844</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10479</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>24595</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11134</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>23966</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21084</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14661</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>29359</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>49361</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>173590</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>160438</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>186253</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>169879</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>158375</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>180044</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>157304</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>180564</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>72,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>173590</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>159682</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>186129</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,53%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>322321</t>
+          <t>324897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>358215</t>
+          <t>360528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38460</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29425</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>47503</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>35239</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26740</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>44072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>27081</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45462</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>22,44%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>38460</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>29589</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>47376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62485</t>
+          <t>62394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85590</t>
+          <t>87370</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13561</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20487</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13186</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8157</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19131</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8268</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20764</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13561</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8465</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35370</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>102863</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>93921</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>114623</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108618</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99061</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118351</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97961</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>102863</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>92687</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>112349</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,41%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198744</t>
+          <t>197083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225518</t>
+          <t>224383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -4490,52 +4490,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46705</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37785</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55956</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36179</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27409</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46333</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28685</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>45973</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46705</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37356</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>56411</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70930</t>
+          <t>69896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96032</t>
+          <t>96003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8761</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14696</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9675</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5644</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15483</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5613</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15577</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8761</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4611</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>14472</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121120</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>111556</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>130480</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>63,17%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>122725</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>111621</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>131757</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>112904</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>130581</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>72,8%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>66,21%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>78,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>121120</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>110369</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>130911</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>68,59%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>228565</t>
+          <t>228980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>257471</t>
+          <t>256876</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,42%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>168579</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>168579</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>168579</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>187178</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>168099</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>206949</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>25,23%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>151808</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>134541</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>170311</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>134546</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>169791</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>21,46%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>187178</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>168533</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>209425</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313839</t>
+          <t>314199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365110</t>
+          <t>366253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60435</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48114</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>73102</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>57543</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46414</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>69469</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>46183</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>70340</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60435</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>73146</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102268</t>
+          <t>102309</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137365</t>
+          <t>136755</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>494160</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>472145</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>515498</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66,62%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>63,65%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>69,5%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>498026</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>479691</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>518918</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>479121</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>517833</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>70,4%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>494160</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>470960</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>513957</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>961615</t>
+          <t>962013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1020835</t>
+          <t>1018349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>707376</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>707376</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>707376</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17601</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12271</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24893</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12908</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8806</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18148</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8623</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19134</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17601</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12243</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24249</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14481</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21661</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10503</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15837</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16040</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>8,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14481</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9344</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22095</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81096</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>96436</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>73,56%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>66,83%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106981</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>99897</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>113485</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>99302</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>112911</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>82,05%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>76,61%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89257</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80812</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>96657</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>73,56%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>184242</t>
+          <t>184079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205565</t>
+          <t>205142</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,49%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121339</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>121339</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>121339</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>130392</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>130392</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>130392</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>121339</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>121339</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>121339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30800</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39122</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>26399</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19396</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34780</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19191</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>34209</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30800</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22776</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39466</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>46431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15564</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>30200</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>13879</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8228</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>8845</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20057</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>22042</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>15600</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>30116</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>26681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45406</t>
+          <t>45640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>201920</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>191104</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>211330</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>166035</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>156276</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>174405</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>157276</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>174895</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>80,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>75,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>201920</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>191154</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>211261</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>79,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353340</t>
+          <t>354677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>380770</t>
+          <t>381095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>254762</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>254762</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>254762</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>206312</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>206312</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>206312</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>254762</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>254762</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>254762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16342</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31822</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32811</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>25023</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41627</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24538</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>42254</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>17,65%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16835</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31879</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>45346</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67863</t>
+          <t>67567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12869</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20126</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22699</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15383</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31376</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15420</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30660</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12869</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8166</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20114</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45953</t>
+          <t>47993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147583</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>156147</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>130408</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>119898</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>140316</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>119661</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>141073</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>70,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>147583</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137693</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>155346</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,24%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263085</t>
+          <t>263431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291069</t>
+          <t>290931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>183925</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>183925</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>183925</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>185919</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>185919</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>185919</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>183925</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>183925</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>183925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24823</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18117</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33047</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>37863</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29699</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47984</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29328</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48137</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,88%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24823</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17849</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>32641</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51426</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76069</t>
+          <t>74332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12297</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7361</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18759</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>10803</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6230</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17378</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6313</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17165</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12297</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>7044</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19057</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -7340,74 +7340,74 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>128423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>118728</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>136550</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>77,58%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>71,72%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>82,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>116838</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>106521</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>126282</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>105544</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>126284</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>70,6%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>63,77%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>76,3%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>128423</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>118862</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>136067</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>71,8%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>340</t>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>230499</t>
+          <t>231063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>256925</t>
+          <t>257901</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>165543</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>165543</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>165543</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>165504</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>165504</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>165504</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>165543</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>165543</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>165543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>96697</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>82070</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>113850</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>109982</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>94185</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>125738</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>94561</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>125295</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>15,98%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>96697</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>83262</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>112009</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>185984</t>
+          <t>185165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226982</t>
+          <t>229681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -7688,67 +7688,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>61689</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49539</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74131</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>57883</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46880</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>70808</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>46867</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>70660</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>8,41%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>61689</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>50527</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>76109</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>104580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137127</t>
+          <t>138082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>567182</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>548657</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>584675</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>786</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>520263</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>500158</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>537504</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>501991</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>539107</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>75,61%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>567182</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>548146</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>584236</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>78,17%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1062684</t>
+          <t>1059297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1111404</t>
+          <t>1109957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>688128</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>688128</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>688128</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
